--- a/master_menu.xlsx
+++ b/master_menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\attaf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F465B06-1EC4-45B7-ABE2-4A0162416A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B97DB81-B3CD-4F8A-B129-E05560CB5158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,7 +691,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
@@ -702,7 +702,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1">
@@ -713,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1">
@@ -724,7 +724,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1">
@@ -735,7 +735,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1">
@@ -828,5 +828,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master_menu.xlsx
+++ b/master_menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\attaf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B97DB81-B3CD-4F8A-B129-E05560CB5158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DACAB8B-F5D8-4EBE-AE36-042D449CEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>es kopi susu vanilla</t>
   </si>
   <si>
-    <t>es kopi susu salted caramel</t>
-  </si>
-  <si>
     <t>es kopi susu pandan</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>snack mix plate</t>
+  </si>
+  <si>
+    <t>es kopi susu salt caramel</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -652,7 +652,7 @@
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -740,29 +740,29 @@
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
@@ -773,57 +773,57 @@
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
